--- a/runs/RELX/2026-10-14/bear/scratch/b_margin_324/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/b_margin_324/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1884.477562098387</v>
+        <v>1937.88536372186</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.103145</v>
+        <v>0.0953618</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.09600960394000001</v>
+        <v>0.089224054516</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>10258.03201005056</v>
+        <v>10413.72366266156</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>35050.16038583209</v>
+        <v>38485.882220967</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>23201.99830865304</v>
+        <v>26198.34997758848</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>33460.0303187036</v>
+        <v>36612.07364025004</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>26463.0303187036</v>
+        <v>29615.07364025004</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>25305.65171950106</v>
+        <v>28532.76399595114</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>14.51216236301624</v>
+        <v>16.36283105310322</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1451.216236301624</v>
+        <v>1636.283105310323</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.4762842886</v>
+        <v>-0.4094972554</v>
       </c>
     </row>
   </sheetData>
